--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIT\Documents\PA_Catts\Nitw_WB\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A356362C-E90A-4F6A-B1F5-C0442C662899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905D1388-1E28-45C1-A361-8B5A14EC9004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="1998" sheetId="12" r:id="rId12"/>
     <sheet name="1999" sheetId="13" r:id="rId13"/>
     <sheet name="2000" sheetId="14" r:id="rId14"/>
-    <sheet name="2001" sheetId="15" r:id="rId15"/>
+    <sheet name="2001" sheetId="30" r:id="rId15"/>
     <sheet name="2003" sheetId="16" r:id="rId16"/>
     <sheet name="2004" sheetId="17" r:id="rId17"/>
     <sheet name="2005" sheetId="18" r:id="rId18"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="346">
   <si>
     <t>Year</t>
   </si>
@@ -1168,9 +1168,6 @@
     <t>B. Raghuram Kadali</t>
   </si>
   <si>
-    <t>Phd_Alumini/S2001/G.V.R Prasada Raju</t>
-  </si>
-  <si>
     <t>Professor in NITW(Civil Engineering)</t>
   </si>
   <si>
@@ -1435,12 +1432,73 @@
 There is ample scope to further improve the model presented in this research by encompassing the issues concerned with Zoning, Calibration of local and long distance travel along with a number of measurement problems associated with them. 
 As there are gaps between the model attempting to explain the travel behaviour and those observed in reality, sincere efforts are required to study the micro level interfacing based on accurate documentation procedures at depot level on cost of operation. </t>
   </si>
+  <si>
+    <t>Phd_Alumini/S2005/K.V.Krishna Reddy</t>
+  </si>
+  <si>
+    <t>Professor in Civil Engineering Department at MVSR Engineering College</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2004/N. Srinivasa Reddy</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2004/B. Raghavendra</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2001/G.V.R. Prasada Raju</t>
+  </si>
+  <si>
+    <r>
+      <t>Professsor  in Department of Civil Engineering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Institute of Road and Transport Technology (IRTT)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Erode, Tamil Nadu, India. </t>
+    </r>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2003/G. Bhaskar</t>
+  </si>
+  <si>
+    <t>Phd_Alumini/S2001/Mohammed Ahmed Ali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transportation Engineering Manager , City of Lethbridge, Canada </t>
+  </si>
+  <si>
+    <t>Professor of Civil Engineering and the former Vice-Chancellor of Jawaharlal Nehru Technological University-Kakinada (JNTUK), Andhra Pradesh, India.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1565,6 +1623,18 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1587,7 +1657,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1632,6 +1702,10 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1914,7 +1988,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="5" width="42.28515625" customWidth="1"/>
@@ -1923,7 +1997,7 @@
     <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1949,7 +2023,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1980</v>
       </c>
@@ -1977,14 +2051,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2010,7 +2084,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1996</v>
       </c>
@@ -2030,13 +2104,13 @@
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -2047,7 +2121,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="44.140625" customWidth="1"/>
@@ -2055,7 +2129,7 @@
     <col min="7" max="7" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2081,7 +2155,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1997</v>
       </c>
@@ -2095,16 +2169,16 @@
         <v>169</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1997</v>
       </c>
@@ -2127,7 +2201,7 @@
         <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2141,13 +2215,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="157.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2173,7 +2247,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1998</v>
       </c>
@@ -2193,13 +2267,13 @@
         <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2" s="24" t="s">
         <v>317</v>
       </c>
-      <c r="H2" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1998</v>
       </c>
@@ -2219,13 +2293,13 @@
         <v>39</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>1998</v>
       </c>
@@ -2245,13 +2319,13 @@
         <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
@@ -2263,12 +2337,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2294,7 +2368,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1999</v>
       </c>
@@ -2322,9 +2396,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2350,7 +2424,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2000</v>
       </c>
@@ -2370,10 +2444,10 @@
         <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2382,14 +2456,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4B9BB0-2B41-49E6-8CFD-B6A8D185801F}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="38.28515625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2415,50 +2486,57 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:8" ht="300">
+      <c r="A2">
         <v>2001</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>267</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="G2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="135">
+      <c r="A3">
         <v>2001</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>344</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2468,13 +2546,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="60.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2500,7 +2578,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="315">
       <c r="A2" s="3">
         <v>2003</v>
       </c>
@@ -2517,11 +2595,11 @@
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2003</v>
       </c>
@@ -2540,7 +2618,12 @@
       <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2550,12 +2633,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="46.5703125" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2581,7 +2665,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2004</v>
       </c>
@@ -2600,9 +2684,11 @@
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2004</v>
       </c>
@@ -2621,7 +2707,9 @@
       <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3" t="s">
+        <v>338</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2631,15 +2719,17 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="8" max="8" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2665,7 +2755,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2005</v>
       </c>
@@ -2684,9 +2774,14 @@
       <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
       <c r="G3" s="2"/>
     </row>
   </sheetData>
@@ -2697,7 +2792,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
@@ -2705,7 +2800,7 @@
     <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2731,7 +2826,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2006</v>
       </c>
@@ -2760,12 +2855,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="5" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +2886,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1982</v>
       </c>
@@ -2825,13 +2920,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="45.5703125" customWidth="1"/>
     <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2857,7 +2952,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2012</v>
       </c>
@@ -2877,10 +2972,10 @@
         <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2891,14 +2986,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="4" max="4" width="30.42578125" customWidth="1"/>
     <col min="5" max="5" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2924,7 +3019,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2018</v>
       </c>
@@ -2944,7 +3039,7 @@
         <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2955,14 +3050,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="138.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2988,7 +3083,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>2019</v>
       </c>
@@ -3011,7 +3106,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2019</v>
       </c>
@@ -3034,7 +3129,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2019</v>
       </c>
@@ -3057,7 +3152,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2019</v>
       </c>
@@ -3077,10 +3172,10 @@
         <v>64</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2019</v>
       </c>
@@ -3100,10 +3195,10 @@
         <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2019</v>
       </c>
@@ -3123,7 +3218,7 @@
         <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +3229,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="56.140625" customWidth="1"/>
@@ -3145,7 +3240,7 @@
     <col min="8" max="8" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3171,7 +3266,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="12">
         <v>2020</v>
       </c>
@@ -3191,10 +3286,10 @@
         <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="12">
         <v>2020</v>
       </c>
@@ -3217,7 +3312,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="12">
         <v>2020</v>
       </c>
@@ -3237,7 +3332,7 @@
         <v>86</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3248,13 +3343,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="5" max="5" width="118.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3280,7 +3375,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -3294,17 +3389,17 @@
         <v>143</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="8">
         <v>2021</v>
       </c>
@@ -3328,7 +3423,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="8">
         <v>2021</v>
       </c>
@@ -3360,7 +3455,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="4" width="41.5703125" customWidth="1"/>
@@ -3368,7 +3463,7 @@
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3394,7 +3489,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.5">
       <c r="A2">
         <v>2022</v>
       </c>
@@ -3417,7 +3512,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>2022</v>
       </c>
@@ -3431,7 +3526,7 @@
         <v>136</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>67</v>
@@ -3440,7 +3535,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4" s="3">
         <v>2022</v>
       </c>
@@ -3460,10 +3555,10 @@
         <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5" s="3">
         <v>2022</v>
       </c>
@@ -3477,7 +3572,7 @@
         <v>138</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -3486,7 +3581,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6" s="3">
         <v>2022</v>
       </c>
@@ -3500,7 +3595,7 @@
         <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>64</v>
@@ -3509,7 +3604,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="409.5">
       <c r="A7" s="3">
         <v>2022</v>
       </c>
@@ -3532,7 +3627,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8" s="3">
         <v>2022</v>
       </c>
@@ -3546,7 +3641,7 @@
         <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>86</v>
@@ -3563,7 +3658,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
@@ -3571,7 +3666,7 @@
     <col min="6" max="6" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3597,7 +3692,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -3614,10 +3709,10 @@
         <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -3640,7 +3735,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -3657,7 +3752,7 @@
         <v>197</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -3668,7 +3763,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.85546875" customWidth="1"/>
     <col min="4" max="4" width="45.5703125" customWidth="1"/>
@@ -3676,7 +3771,7 @@
     <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3702,7 +3797,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -3716,7 +3811,7 @@
         <v>116</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
         <v>186</v>
@@ -3725,7 +3820,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -3736,7 +3831,7 @@
         <v>117</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F3" t="s">
         <v>186</v>
@@ -3745,7 +3840,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -3759,7 +3854,7 @@
         <v>118</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F4" t="s">
         <v>192</v>
@@ -3768,7 +3863,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -3788,7 +3883,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2024</v>
       </c>
@@ -3796,7 +3891,7 @@
         <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
         <v>120</v>
@@ -3808,30 +3903,30 @@
         <v>186</v>
       </c>
       <c r="G6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D7" t="s">
         <v>121</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7" t="s">
         <v>186</v>
       </c>
       <c r="G7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="409.5">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -3845,7 +3940,7 @@
         <v>122</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F8" t="s">
         <v>184</v>
@@ -3862,7 +3957,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="54" customWidth="1"/>
@@ -3872,7 +3967,7 @@
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3898,7 +3993,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -3909,7 +4004,7 @@
         <v>132</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F2" t="s">
         <v>184</v>
@@ -3918,7 +4013,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -3932,7 +4027,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" t="s">
         <v>182</v>
@@ -3941,7 +4036,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="409.5">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -3955,7 +4050,7 @@
         <v>134</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F4" t="s">
         <v>182</v>
@@ -3964,7 +4059,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="409.5">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -3978,7 +4073,7 @@
         <v>222</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>272</v>
@@ -3987,24 +4082,24 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5">
       <c r="A6">
         <v>2025</v>
       </c>
       <c r="B6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>288</v>
-      </c>
       <c r="G6" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4018,14 +4113,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="38.140625" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4051,27 +4146,27 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="G2" s="23" t="s">
         <v>309</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4085,12 +4180,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="48.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4116,7 +4211,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1983</v>
       </c>
@@ -4136,10 +4231,10 @@
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4150,13 +4245,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4182,7 +4277,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1984</v>
       </c>
@@ -4202,7 +4297,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4213,9 +4308,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4241,7 +4336,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1985</v>
       </c>
@@ -4261,10 +4356,10 @@
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4275,12 +4370,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="93.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4306,7 +4401,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1986</v>
       </c>
@@ -4334,9 +4429,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4362,7 +4457,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1988</v>
       </c>
@@ -4390,7 +4485,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
@@ -4399,7 +4494,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4425,7 +4520,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="90">
       <c r="A2" s="3">
         <v>1989</v>
       </c>
@@ -4443,7 +4538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="409.5">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -4471,7 +4566,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -4479,7 +4574,7 @@
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4505,7 +4600,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="409.5">
       <c r="A2" s="3">
         <v>1992</v>
       </c>
@@ -4525,7 +4620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="409.5">
       <c r="A3" s="3">
         <v>1992</v>
       </c>
@@ -4539,16 +4634,16 @@
         <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/excels/Phd_Alumini.xlsx
+++ b/excels/Phd_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIT\Documents\PA_Catts\Nitw_WB\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905D1388-1E28-45C1-A361-8B5A14EC9004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF4E12A-146A-496E-91FC-32915CA279D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1980" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,22 @@
     <sheet name="2025" sheetId="28" r:id="rId28"/>
     <sheet name="2026" sheetId="29" r:id="rId29"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -56,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="354">
   <si>
     <t>Year</t>
   </si>
@@ -1492,6 +1504,32 @@
   </si>
   <si>
     <t>Professor of Civil Engineering and the former Vice-Chancellor of Jawaharlal Nehru Technological University-Kakinada (JNTUK), Andhra Pradesh, India.</t>
+  </si>
+  <si>
+    <t>Ammu B C</t>
+  </si>
+  <si>
+    <t>Full depth reclamation mixes</t>
+  </si>
+  <si>
+    <t>Raji Reddy Myakala</t>
+  </si>
+  <si>
+    <t>Prof. S. Shankar</t>
+  </si>
+  <si>
+    <t>Prof. Vishnu R.</t>
+  </si>
+  <si>
+    <t>Phd_Current/Ammu</t>
+  </si>
+  <si>
+    <t>Phd_Current/Raji Reddy Myakala</t>
+  </si>
+  <si>
+    <t>Efficient road transport is vital for a country's economic growth, supporting regional integration and socio-economic progress. India has an extensive, flexible network reaching remote areas,with over 7 million km of roads, 73% of which are Low-Volume Rural Roads (LVRRs). These connect villages, markets, healthcare, and schools, promoting rural development. Since 2000, the Indian government has invested in rural infrastructure through the “Pradhan Mantri Gram Sadak Yojana (PMGSY), " but maintenance is traditional, lacking detailed performance assessments. Growing traffic, climate change, resource scarcity, and ageing infrastructure demand a shift from reactive repairs to sustainability-focused pavement management, aiming to balance economic, environmental, and social factors, optimize repairs, extend pavement life, cut costs and emissions, and build resilient rural roads.
+This research develops a QBL-based sustainability rating framework for LVRRs in India, integrating economic, environmental, social, and pavement performance dimensions for holistic decision-making. It identifies sustainability indicators via literature, expert input, and stakeholder interactions, classifying them into criteria and sub-criteria under QBL. The Analytical Hierarchy Process (AHP) determines indicator importance through expert pairwise comparisons, ensuring consistency. Based on these weights, two decision-support systems are created: the EESM-SAI Tool for evaluating rural road maintenance and the SPMT-AI Tool for ranking and recommending pavement treatment options. The methodology combines engineering, environmental, social, management, and material factors into a unified framework for transparent, scientifically sound decisions.
+The framework, validated through case studies and sensitivity analyses of Telangana's LVRRS,demonstrates that incorporating pavement performance alongside economic, environmental,and social considerations leads to better maintenance planning. It improves resource use,prolongs pavement durability, reduces costs, minimises environmental impact, and enhancesrural accessibility and resilience. Providing a scientific, objective tool, it helps agencies and policymakers plan sustainable maintenance within budget constraints. This research presents a new sustainability assessment method for LVRRs based on the QBL approach, integrating engineering with sustainability principles. The framework supports policy development, optimises maintenance strategies, and promotes resilient, cost-effective, and environmentally friendly rural roads, contributing to sustainable rural development in India.</t>
   </si>
 </sst>
 </file>
@@ -1631,9 +1669,9 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color rgb="FF162C5B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1657,7 +1695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1706,6 +1744,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4112,12 +4159,13 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="38.140625" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
@@ -4167,6 +4215,43 @@
       </c>
       <c r="G2" s="23" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="409.5">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
